--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121859682</v>
+        <v>121859676</v>
       </c>
       <c r="B5" t="n">
-        <v>97114</v>
+        <v>8436</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221946</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>687243</v>
+        <v>687355</v>
       </c>
       <c r="R5" t="n">
-        <v>6563593</v>
+        <v>6563585</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,6 +1119,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1135,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121859676</v>
+        <v>121859682</v>
       </c>
       <c r="B6" t="n">
-        <v>8436</v>
+        <v>97116</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,21 +1166,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>221946</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1175,10 +1190,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>687355</v>
+        <v>687243</v>
       </c>
       <c r="R6" t="n">
-        <v>6563585</v>
+        <v>6563593</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1225,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1220,7 +1235,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,21 +1246,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1265,7 +1265,7 @@
         <v>121859683</v>
       </c>
       <c r="B7" t="n">
-        <v>97111</v>
+        <v>97113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121859680</v>
+        <v>121859677</v>
       </c>
       <c r="B8" t="n">
-        <v>97117</v>
+        <v>95706</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,25 +1386,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687241</v>
+        <v>687329</v>
       </c>
       <c r="R8" t="n">
-        <v>6563587</v>
+        <v>6563566</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,10 +1486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121859677</v>
+        <v>121859680</v>
       </c>
       <c r="B9" t="n">
-        <v>95704</v>
+        <v>97119</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,25 +1498,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>687329</v>
+        <v>687241</v>
       </c>
       <c r="R9" t="n">
-        <v>6563566</v>
+        <v>6563587</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121859676</v>
+        <v>121859680</v>
       </c>
       <c r="B5" t="n">
-        <v>8436</v>
+        <v>97119</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>687355</v>
+        <v>687241</v>
       </c>
       <c r="R5" t="n">
-        <v>6563585</v>
+        <v>6563587</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,21 +1119,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1150,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121859682</v>
+        <v>121859677</v>
       </c>
       <c r="B6" t="n">
-        <v>97116</v>
+        <v>95706</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,25 +1147,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221946</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1190,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>687243</v>
+        <v>687329</v>
       </c>
       <c r="R6" t="n">
-        <v>6563593</v>
+        <v>6563566</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,7 +1210,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,7 +1220,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,10 +1247,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121859683</v>
+        <v>121859682</v>
       </c>
       <c r="B7" t="n">
-        <v>97113</v>
+        <v>97116</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,16 +1263,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>221946</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1374,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121859677</v>
+        <v>121859676</v>
       </c>
       <c r="B8" t="n">
-        <v>95706</v>
+        <v>8436</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,25 +1371,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1414,10 +1399,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687329</v>
+        <v>687355</v>
       </c>
       <c r="R8" t="n">
-        <v>6563566</v>
+        <v>6563585</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1449,7 +1434,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1459,7 +1444,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,6 +1455,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1486,10 +1486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121859680</v>
+        <v>121859683</v>
       </c>
       <c r="B9" t="n">
-        <v>97119</v>
+        <v>97113</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1502,16 +1502,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>687241</v>
+        <v>687243</v>
       </c>
       <c r="R9" t="n">
-        <v>6563587</v>
+        <v>6563593</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121859683</v>
+        <v>121859682</v>
       </c>
       <c r="B5" t="n">
-        <v>97129</v>
+        <v>97132</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,16 +1039,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>221946</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121859676</v>
+        <v>121859680</v>
       </c>
       <c r="B6" t="n">
-        <v>8436</v>
+        <v>97135</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,21 +1151,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>687355</v>
+        <v>687241</v>
       </c>
       <c r="R6" t="n">
-        <v>6563585</v>
+        <v>6563587</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,21 +1231,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1262,10 +1247,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121859677</v>
+        <v>121859676</v>
       </c>
       <c r="B7" t="n">
-        <v>95722</v>
+        <v>8436</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,25 +1259,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1302,10 +1287,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687329</v>
+        <v>687355</v>
       </c>
       <c r="R7" t="n">
-        <v>6563566</v>
+        <v>6563585</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,7 +1332,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,6 +1343,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1374,10 +1374,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121859680</v>
+        <v>121859683</v>
       </c>
       <c r="B8" t="n">
-        <v>97135</v>
+        <v>97129</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1390,16 +1390,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687241</v>
+        <v>687243</v>
       </c>
       <c r="R8" t="n">
-        <v>6563587</v>
+        <v>6563593</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,10 +1486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121859682</v>
+        <v>121859677</v>
       </c>
       <c r="B9" t="n">
-        <v>97132</v>
+        <v>95722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,25 +1498,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221946</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>687243</v>
+        <v>687329</v>
       </c>
       <c r="R9" t="n">
-        <v>6563593</v>
+        <v>6563566</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1596,6 +1596,942 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126004805</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98248</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>687448</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6563548</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126004260</v>
+      </c>
+      <c r="B11" t="n">
+        <v>105355</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>687243</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6563585</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126004158</v>
+      </c>
+      <c r="B12" t="n">
+        <v>95780</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>210</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>687335</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6563581</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Mogna och uppsprickande kapslar.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126004216</v>
+      </c>
+      <c r="B13" t="n">
+        <v>105355</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>687301</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6563579</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126004817</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98248</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>687473</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6563539</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126004295</v>
+      </c>
+      <c r="B15" t="n">
+        <v>105355</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>687291</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6563610</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126004787</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58479</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>687399</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6563564</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126004534</v>
+      </c>
+      <c r="B17" t="n">
+        <v>105355</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>knoppbristning</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>687349</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6563661</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126004770</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98248</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>687399</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6563564</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>126004805</v>
       </c>
       <c r="B10" t="n">
-        <v>98248</v>
+        <v>98249</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>126004260</v>
       </c>
       <c r="B11" t="n">
-        <v>105355</v>
+        <v>105356</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>126004158</v>
       </c>
       <c r="B12" t="n">
-        <v>95780</v>
+        <v>95781</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>126004216</v>
       </c>
       <c r="B13" t="n">
-        <v>105355</v>
+        <v>105356</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>126004817</v>
       </c>
       <c r="B14" t="n">
-        <v>98248</v>
+        <v>98249</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>126004295</v>
       </c>
       <c r="B15" t="n">
-        <v>105355</v>
+        <v>105356</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>126004787</v>
       </c>
       <c r="B16" t="n">
-        <v>58479</v>
+        <v>58480</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126004534</v>
+        <v>126004770</v>
       </c>
       <c r="B17" t="n">
-        <v>105355</v>
+        <v>98249</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2337,30 +2337,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>knoppbristning</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2369,10 +2365,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>687349</v>
+        <v>687399</v>
       </c>
       <c r="R17" t="n">
-        <v>6563661</v>
+        <v>6563564</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2432,10 +2428,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126004770</v>
+        <v>126004534</v>
       </c>
       <c r="B18" t="n">
-        <v>98248</v>
+        <v>105356</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2443,26 +2439,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>knoppbristning</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>687399</v>
+        <v>687349</v>
       </c>
       <c r="R18" t="n">
-        <v>6563564</v>
+        <v>6563661</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>126004805</v>
       </c>
       <c r="B10" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>126004260</v>
       </c>
       <c r="B11" t="n">
-        <v>105356</v>
+        <v>105358</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>126004158</v>
       </c>
       <c r="B12" t="n">
-        <v>95781</v>
+        <v>95783</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>126004216</v>
       </c>
       <c r="B13" t="n">
-        <v>105356</v>
+        <v>105358</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>126004817</v>
       </c>
       <c r="B14" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>126004295</v>
       </c>
       <c r="B15" t="n">
-        <v>105356</v>
+        <v>105358</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126004770</v>
+        <v>126004534</v>
       </c>
       <c r="B17" t="n">
-        <v>98249</v>
+        <v>105358</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2337,26 +2337,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>knoppbristning</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2365,10 +2369,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>687399</v>
+        <v>687349</v>
       </c>
       <c r="R17" t="n">
-        <v>6563564</v>
+        <v>6563661</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2428,10 +2432,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126004534</v>
+        <v>126004770</v>
       </c>
       <c r="B18" t="n">
-        <v>105356</v>
+        <v>98251</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2439,30 +2443,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>knoppbristning</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>687349</v>
+        <v>687399</v>
       </c>
       <c r="R18" t="n">
-        <v>6563661</v>
+        <v>6563564</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2532,6 +2532,215 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126079502</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97216</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>687453</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6563526</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt i kärret.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126079446</v>
+      </c>
+      <c r="B20" t="n">
+        <v>95941</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>687416</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6563568</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>126004805</v>
       </c>
       <c r="B10" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>126004260</v>
       </c>
       <c r="B11" t="n">
-        <v>105358</v>
+        <v>105362</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>126004158</v>
       </c>
       <c r="B12" t="n">
-        <v>95783</v>
+        <v>95787</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>126004216</v>
       </c>
       <c r="B13" t="n">
-        <v>105358</v>
+        <v>105362</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>126004817</v>
       </c>
       <c r="B14" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>126004295</v>
       </c>
       <c r="B15" t="n">
-        <v>105358</v>
+        <v>105362</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>126004534</v>
       </c>
       <c r="B17" t="n">
-        <v>105358</v>
+        <v>105362</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>126004770</v>
       </c>
       <c r="B18" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>126004805</v>
       </c>
       <c r="B10" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>126004260</v>
       </c>
       <c r="B11" t="n">
-        <v>105362</v>
+        <v>105363</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>126004158</v>
       </c>
       <c r="B12" t="n">
-        <v>95787</v>
+        <v>95788</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>126004216</v>
       </c>
       <c r="B13" t="n">
-        <v>105362</v>
+        <v>105363</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>126004817</v>
       </c>
       <c r="B14" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>126004295</v>
       </c>
       <c r="B15" t="n">
-        <v>105362</v>
+        <v>105363</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>126004534</v>
       </c>
       <c r="B17" t="n">
-        <v>105362</v>
+        <v>105363</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>126004770</v>
       </c>
       <c r="B18" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>126079502</v>
       </c>
       <c r="B19" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>126079446</v>
       </c>
       <c r="B20" t="n">
-        <v>95941</v>
+        <v>95942</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -1802,10 +1802,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126004158</v>
+        <v>126004216</v>
       </c>
       <c r="B12" t="n">
-        <v>95788</v>
+        <v>105363</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1813,34 +1813,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>210</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1849,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>687335</v>
+        <v>687301</v>
       </c>
       <c r="R12" t="n">
-        <v>6563581</v>
+        <v>6563579</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1885,11 +1877,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Mogna och uppsprickande kapslar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,10 +1904,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126004216</v>
+        <v>126004158</v>
       </c>
       <c r="B13" t="n">
-        <v>105363</v>
+        <v>95788</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1928,26 +1915,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>210</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1956,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>687301</v>
+        <v>687335</v>
       </c>
       <c r="R13" t="n">
-        <v>6563579</v>
+        <v>6563581</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1992,6 +1987,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Mogna och uppsprickande kapslar.</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1601,7 +1601,7 @@
         <v>126004805</v>
       </c>
       <c r="B10" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>126004260</v>
       </c>
       <c r="B11" t="n">
-        <v>105363</v>
+        <v>105365</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126004216</v>
+        <v>126004158</v>
       </c>
       <c r="B12" t="n">
-        <v>105363</v>
+        <v>95790</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1813,26 +1813,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>210</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1841,10 +1849,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>687301</v>
+        <v>687335</v>
       </c>
       <c r="R12" t="n">
-        <v>6563579</v>
+        <v>6563581</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,6 +1885,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Mogna och uppsprickande kapslar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1904,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126004158</v>
+        <v>126004216</v>
       </c>
       <c r="B13" t="n">
-        <v>95788</v>
+        <v>105365</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1915,34 +1928,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>210</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1951,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>687335</v>
+        <v>687301</v>
       </c>
       <c r="R13" t="n">
-        <v>6563581</v>
+        <v>6563579</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,11 +1992,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Mogna och uppsprickande kapslar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,7 +2022,7 @@
         <v>126004817</v>
       </c>
       <c r="B14" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>126004295</v>
       </c>
       <c r="B15" t="n">
-        <v>105363</v>
+        <v>105365</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>126004787</v>
       </c>
       <c r="B16" t="n">
-        <v>58480</v>
+        <v>58481</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>126004534</v>
       </c>
       <c r="B17" t="n">
-        <v>105363</v>
+        <v>105365</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>126004770</v>
       </c>
       <c r="B18" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>126079502</v>
       </c>
       <c r="B19" t="n">
-        <v>97217</v>
+        <v>97219</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>126079446</v>
       </c>
       <c r="B20" t="n">
-        <v>95942</v>
+        <v>95944</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2741,6 +2741,116 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126212282</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98341</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>687344</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6563653</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2743,57 +2743,61 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126212282</v>
+        <v>126234839</v>
       </c>
       <c r="B21" t="n">
-        <v>98341</v>
+        <v>98364</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Vargklova mosse S om, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>687344</v>
+        <v>687489</v>
       </c>
       <c r="R21" t="n">
-        <v>6563653</v>
+        <v>6563516</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2820,12 +2824,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2841,15 +2845,239 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
+          <t>Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Ulf Johansson, Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126212282</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98343</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>687344</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6563653</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
           <t>Bodil Ravn</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
+      <c r="AX22" t="inlineStr">
         <is>
           <t>Bodil Ravn</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126234886</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98364</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Vargklova mosse S om, Srm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>687464</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6563531</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Ulf Johansson, Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>126004805</v>
       </c>
       <c r="B10" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>126004260</v>
       </c>
       <c r="B11" t="n">
-        <v>105365</v>
+        <v>105367</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>126004158</v>
       </c>
       <c r="B12" t="n">
-        <v>95790</v>
+        <v>95792</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>126004216</v>
       </c>
       <c r="B13" t="n">
-        <v>105365</v>
+        <v>105367</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>126004817</v>
       </c>
       <c r="B14" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>126004295</v>
       </c>
       <c r="B15" t="n">
-        <v>105365</v>
+        <v>105367</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126004534</v>
+        <v>126004770</v>
       </c>
       <c r="B17" t="n">
-        <v>105365</v>
+        <v>98260</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2337,30 +2337,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>knoppbristning</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2369,10 +2365,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>687349</v>
+        <v>687399</v>
       </c>
       <c r="R17" t="n">
-        <v>6563661</v>
+        <v>6563564</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2432,10 +2428,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126004770</v>
+        <v>126004534</v>
       </c>
       <c r="B18" t="n">
-        <v>98258</v>
+        <v>105367</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2443,26 +2439,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>knoppbristning</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>687399</v>
+        <v>687349</v>
       </c>
       <c r="R18" t="n">
-        <v>6563564</v>
+        <v>6563661</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2537,7 +2537,7 @@
         <v>126079502</v>
       </c>
       <c r="B19" t="n">
-        <v>97219</v>
+        <v>97221</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>126079446</v>
       </c>
       <c r="B20" t="n">
-        <v>95944</v>
+        <v>95946</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -1802,10 +1802,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126004158</v>
+        <v>126004216</v>
       </c>
       <c r="B12" t="n">
-        <v>95792</v>
+        <v>105367</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1813,34 +1813,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>210</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1849,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>687335</v>
+        <v>687301</v>
       </c>
       <c r="R12" t="n">
-        <v>6563581</v>
+        <v>6563579</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1885,11 +1877,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Mogna och uppsprickande kapslar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,10 +1904,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126004216</v>
+        <v>126004158</v>
       </c>
       <c r="B13" t="n">
-        <v>105367</v>
+        <v>95792</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1928,26 +1915,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>210</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1956,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>687301</v>
+        <v>687335</v>
       </c>
       <c r="R13" t="n">
-        <v>6563579</v>
+        <v>6563581</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1992,6 +1987,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Mogna och uppsprickande kapslar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2326,10 +2326,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126004770</v>
+        <v>126004534</v>
       </c>
       <c r="B17" t="n">
-        <v>98260</v>
+        <v>105367</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2337,26 +2337,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>knoppbristning</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2365,10 +2369,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>687399</v>
+        <v>687349</v>
       </c>
       <c r="R17" t="n">
-        <v>6563564</v>
+        <v>6563661</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2428,10 +2432,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126004534</v>
+        <v>126004770</v>
       </c>
       <c r="B18" t="n">
-        <v>105367</v>
+        <v>98260</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2439,30 +2443,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>knoppbristning</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>687349</v>
+        <v>687399</v>
       </c>
       <c r="R18" t="n">
-        <v>6563661</v>
+        <v>6563564</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>126004805</v>
       </c>
       <c r="B10" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>126004260</v>
       </c>
       <c r="B11" t="n">
-        <v>105367</v>
+        <v>105371</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126004216</v>
+        <v>126004158</v>
       </c>
       <c r="B12" t="n">
-        <v>105367</v>
+        <v>95794</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1813,26 +1813,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>210</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1841,10 +1849,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>687301</v>
+        <v>687335</v>
       </c>
       <c r="R12" t="n">
-        <v>6563579</v>
+        <v>6563581</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,6 +1885,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Mogna och uppsprickande kapslar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1904,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126004158</v>
+        <v>126004216</v>
       </c>
       <c r="B13" t="n">
-        <v>95792</v>
+        <v>105371</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1915,34 +1928,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>210</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1951,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>687335</v>
+        <v>687301</v>
       </c>
       <c r="R13" t="n">
-        <v>6563581</v>
+        <v>6563579</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,11 +1992,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Mogna och uppsprickande kapslar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,7 +2022,7 @@
         <v>126004817</v>
       </c>
       <c r="B14" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>126004295</v>
       </c>
       <c r="B15" t="n">
-        <v>105367</v>
+        <v>105371</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126004534</v>
+        <v>126004770</v>
       </c>
       <c r="B17" t="n">
-        <v>105367</v>
+        <v>98262</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2337,30 +2337,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>knoppbristning</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2369,10 +2365,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>687349</v>
+        <v>687399</v>
       </c>
       <c r="R17" t="n">
-        <v>6563661</v>
+        <v>6563564</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2432,10 +2428,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126004770</v>
+        <v>126004534</v>
       </c>
       <c r="B18" t="n">
-        <v>98260</v>
+        <v>105371</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2443,26 +2439,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>knoppbristning</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>687399</v>
+        <v>687349</v>
       </c>
       <c r="R18" t="n">
-        <v>6563564</v>
+        <v>6563661</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2537,7 +2537,7 @@
         <v>126079502</v>
       </c>
       <c r="B19" t="n">
-        <v>97221</v>
+        <v>97223</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>126079446</v>
       </c>
       <c r="B20" t="n">
-        <v>95946</v>
+        <v>95948</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>126234839</v>
       </c>
       <c r="B21" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>126212282</v>
       </c>
       <c r="B22" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>126234886</v>
       </c>
       <c r="B23" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>126004805</v>
       </c>
       <c r="B10" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>126004260</v>
       </c>
       <c r="B11" t="n">
-        <v>105371</v>
+        <v>105384</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>126004158</v>
       </c>
       <c r="B12" t="n">
-        <v>95794</v>
+        <v>95798</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>126004216</v>
       </c>
       <c r="B13" t="n">
-        <v>105371</v>
+        <v>105384</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>126004817</v>
       </c>
       <c r="B14" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>126004295</v>
       </c>
       <c r="B15" t="n">
-        <v>105371</v>
+        <v>105384</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>126004787</v>
       </c>
       <c r="B16" t="n">
-        <v>58481</v>
+        <v>58485</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>126004770</v>
       </c>
       <c r="B17" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>126004534</v>
       </c>
       <c r="B18" t="n">
-        <v>105371</v>
+        <v>105384</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>126079502</v>
       </c>
       <c r="B19" t="n">
-        <v>97223</v>
+        <v>97227</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>126079446</v>
       </c>
       <c r="B20" t="n">
-        <v>95948</v>
+        <v>95952</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>126234839</v>
       </c>
       <c r="B21" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>126212282</v>
       </c>
       <c r="B22" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>126234886</v>
       </c>
       <c r="B23" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -1802,10 +1802,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126004158</v>
+        <v>126004216</v>
       </c>
       <c r="B12" t="n">
-        <v>95798</v>
+        <v>105384</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1813,34 +1813,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>210</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1849,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>687335</v>
+        <v>687301</v>
       </c>
       <c r="R12" t="n">
-        <v>6563581</v>
+        <v>6563579</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1885,11 +1877,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Mogna och uppsprickande kapslar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,10 +1904,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126004216</v>
+        <v>126004158</v>
       </c>
       <c r="B13" t="n">
-        <v>105384</v>
+        <v>95798</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1928,26 +1915,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>210</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1956,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>687301</v>
+        <v>687335</v>
       </c>
       <c r="R13" t="n">
-        <v>6563579</v>
+        <v>6563581</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1992,6 +1987,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Mogna och uppsprickande kapslar.</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>126004805</v>
       </c>
       <c r="B10" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>126004260</v>
       </c>
       <c r="B11" t="n">
-        <v>105384</v>
+        <v>105387</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126004216</v>
+        <v>126004158</v>
       </c>
       <c r="B12" t="n">
-        <v>105384</v>
+        <v>95801</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1813,26 +1813,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>210</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1841,10 +1849,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>687301</v>
+        <v>687335</v>
       </c>
       <c r="R12" t="n">
-        <v>6563579</v>
+        <v>6563581</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,6 +1885,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Mogna och uppsprickande kapslar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1904,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126004158</v>
+        <v>126004216</v>
       </c>
       <c r="B13" t="n">
-        <v>95798</v>
+        <v>105387</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1915,34 +1928,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>210</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1951,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>687335</v>
+        <v>687301</v>
       </c>
       <c r="R13" t="n">
-        <v>6563581</v>
+        <v>6563579</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,11 +1992,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Mogna och uppsprickande kapslar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,7 +2022,7 @@
         <v>126004817</v>
       </c>
       <c r="B14" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>126004295</v>
       </c>
       <c r="B15" t="n">
-        <v>105384</v>
+        <v>105387</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>126004770</v>
       </c>
       <c r="B17" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>126004534</v>
       </c>
       <c r="B18" t="n">
-        <v>105384</v>
+        <v>105387</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>126079502</v>
       </c>
       <c r="B19" t="n">
-        <v>97227</v>
+        <v>97230</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>126079446</v>
       </c>
       <c r="B20" t="n">
-        <v>95952</v>
+        <v>95955</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>126234839</v>
       </c>
       <c r="B21" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>126212282</v>
       </c>
       <c r="B22" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>126234886</v>
       </c>
       <c r="B23" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3079,6 +3079,111 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126419167</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57816</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>687410</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6563618</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -2326,10 +2326,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126004770</v>
+        <v>126004534</v>
       </c>
       <c r="B17" t="n">
-        <v>98269</v>
+        <v>105387</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2337,26 +2337,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>knoppbristning</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2365,10 +2369,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>687399</v>
+        <v>687349</v>
       </c>
       <c r="R17" t="n">
-        <v>6563564</v>
+        <v>6563661</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2428,10 +2432,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126004534</v>
+        <v>126004770</v>
       </c>
       <c r="B18" t="n">
-        <v>105387</v>
+        <v>98269</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2439,30 +2443,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>knoppbristning</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>687349</v>
+        <v>687399</v>
       </c>
       <c r="R18" t="n">
-        <v>6563661</v>
+        <v>6563564</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -2326,10 +2326,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126004534</v>
+        <v>126004770</v>
       </c>
       <c r="B17" t="n">
-        <v>105387</v>
+        <v>98269</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2337,30 +2337,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>knoppbristning</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2369,10 +2365,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>687349</v>
+        <v>687399</v>
       </c>
       <c r="R17" t="n">
-        <v>6563661</v>
+        <v>6563564</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2432,10 +2428,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126004770</v>
+        <v>126004534</v>
       </c>
       <c r="B18" t="n">
-        <v>98269</v>
+        <v>105387</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2443,26 +2439,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>knoppbristning</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>687399</v>
+        <v>687349</v>
       </c>
       <c r="R18" t="n">
-        <v>6563564</v>
+        <v>6563661</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>126004805</v>
       </c>
       <c r="B10" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>126004260</v>
       </c>
       <c r="B11" t="n">
-        <v>105387</v>
+        <v>105396</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>126004158</v>
       </c>
       <c r="B12" t="n">
-        <v>95801</v>
+        <v>95810</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>126004216</v>
       </c>
       <c r="B13" t="n">
-        <v>105387</v>
+        <v>105396</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>126004817</v>
       </c>
       <c r="B14" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>126004295</v>
       </c>
       <c r="B15" t="n">
-        <v>105387</v>
+        <v>105396</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>126004787</v>
       </c>
       <c r="B16" t="n">
-        <v>58485</v>
+        <v>58488</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126004770</v>
+        <v>126004534</v>
       </c>
       <c r="B17" t="n">
-        <v>98269</v>
+        <v>105396</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2337,26 +2337,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>knoppbristning</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2365,10 +2369,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>687399</v>
+        <v>687349</v>
       </c>
       <c r="R17" t="n">
-        <v>6563564</v>
+        <v>6563661</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2428,10 +2432,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126004534</v>
+        <v>126004770</v>
       </c>
       <c r="B18" t="n">
-        <v>105387</v>
+        <v>98278</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2439,30 +2443,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>knoppbristning</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>687349</v>
+        <v>687399</v>
       </c>
       <c r="R18" t="n">
-        <v>6563661</v>
+        <v>6563564</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2537,7 +2537,7 @@
         <v>126079502</v>
       </c>
       <c r="B19" t="n">
-        <v>97230</v>
+        <v>97239</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>126079446</v>
       </c>
       <c r="B20" t="n">
-        <v>95955</v>
+        <v>95964</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>126234839</v>
       </c>
       <c r="B21" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>126212282</v>
       </c>
       <c r="B22" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>126234886</v>
       </c>
       <c r="B23" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>126419167</v>
       </c>
       <c r="B24" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -2326,10 +2326,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126004534</v>
+        <v>126004770</v>
       </c>
       <c r="B17" t="n">
-        <v>105396</v>
+        <v>98278</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2337,30 +2337,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>knoppbristning</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2369,10 +2365,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>687349</v>
+        <v>687399</v>
       </c>
       <c r="R17" t="n">
-        <v>6563661</v>
+        <v>6563564</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2432,10 +2428,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126004770</v>
+        <v>126004534</v>
       </c>
       <c r="B18" t="n">
-        <v>98278</v>
+        <v>105396</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2443,26 +2439,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>knoppbristning</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>687399</v>
+        <v>687349</v>
       </c>
       <c r="R18" t="n">
-        <v>6563564</v>
+        <v>6563661</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -1802,10 +1802,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126004158</v>
+        <v>126004216</v>
       </c>
       <c r="B12" t="n">
-        <v>95810</v>
+        <v>105396</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1813,34 +1813,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>210</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1849,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>687335</v>
+        <v>687301</v>
       </c>
       <c r="R12" t="n">
-        <v>6563581</v>
+        <v>6563579</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1885,11 +1877,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Mogna och uppsprickande kapslar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,10 +1904,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126004216</v>
+        <v>126004158</v>
       </c>
       <c r="B13" t="n">
-        <v>105396</v>
+        <v>95810</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1928,26 +1915,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>210</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1956,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>687301</v>
+        <v>687335</v>
       </c>
       <c r="R13" t="n">
-        <v>6563579</v>
+        <v>6563581</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1992,6 +1987,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Mogna och uppsprickande kapslar.</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3184,6 +3184,405 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128398377</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92642</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>687458</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6563552</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128398269</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92063</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>757</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hapalopilus aurantiacus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>687417</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6563548</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128398996</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91990</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>687317</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6563634</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128398408</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92680</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1968</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Grantaggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Phellodon violascens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>687462</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6563544</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -3287,27 +3287,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128398269</v>
+        <v>128398996</v>
       </c>
       <c r="B26" t="n">
-        <v>92063</v>
+        <v>91990</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>757</v>
+        <v>6031</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3320,10 +3325,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687417</v>
+        <v>687317</v>
       </c>
       <c r="R26" t="n">
-        <v>6563548</v>
+        <v>6563634</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3383,32 +3388,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128398996</v>
+        <v>128398408</v>
       </c>
       <c r="B27" t="n">
-        <v>91990</v>
+        <v>92680</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6031</v>
+        <v>1968</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3421,10 +3426,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>687317</v>
+        <v>687462</v>
       </c>
       <c r="R27" t="n">
-        <v>6563634</v>
+        <v>6563544</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3484,10 +3489,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128398408</v>
+        <v>128398269</v>
       </c>
       <c r="B28" t="n">
-        <v>92680</v>
+        <v>92063</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3495,21 +3500,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1968</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Grantaggsvamp</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3522,10 +3522,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>687462</v>
+        <v>687417</v>
       </c>
       <c r="R28" t="n">
-        <v>6563544</v>
+        <v>6563548</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -3189,7 +3189,7 @@
         <v>128398377</v>
       </c>
       <c r="B25" t="n">
-        <v>92642</v>
+        <v>92644</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>128398996</v>
       </c>
       <c r="B26" t="n">
-        <v>91990</v>
+        <v>91992</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>128398408</v>
       </c>
       <c r="B27" t="n">
-        <v>92680</v>
+        <v>92682</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>128398269</v>
       </c>
       <c r="B28" t="n">
-        <v>92063</v>
+        <v>92065</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -3189,7 +3189,7 @@
         <v>128398377</v>
       </c>
       <c r="B25" t="n">
-        <v>92644</v>
+        <v>92736</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3287,32 +3287,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128398996</v>
+        <v>128398408</v>
       </c>
       <c r="B26" t="n">
-        <v>91992</v>
+        <v>92774</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6031</v>
+        <v>1968</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687317</v>
+        <v>687462</v>
       </c>
       <c r="R26" t="n">
-        <v>6563634</v>
+        <v>6563544</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3388,32 +3388,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128398408</v>
+        <v>128398996</v>
       </c>
       <c r="B27" t="n">
-        <v>92682</v>
+        <v>92084</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1968</v>
+        <v>6031</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>687462</v>
+        <v>687317</v>
       </c>
       <c r="R27" t="n">
-        <v>6563544</v>
+        <v>6563634</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3492,7 +3492,7 @@
         <v>128398269</v>
       </c>
       <c r="B28" t="n">
-        <v>92065</v>
+        <v>92157</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -3287,32 +3287,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128398408</v>
+        <v>128398996</v>
       </c>
       <c r="B26" t="n">
-        <v>92774</v>
+        <v>92084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1968</v>
+        <v>6031</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687462</v>
+        <v>687317</v>
       </c>
       <c r="R26" t="n">
-        <v>6563544</v>
+        <v>6563634</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3388,32 +3388,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128398996</v>
+        <v>128398408</v>
       </c>
       <c r="B27" t="n">
-        <v>92084</v>
+        <v>92774</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6031</v>
+        <v>1968</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>687317</v>
+        <v>687462</v>
       </c>
       <c r="R27" t="n">
-        <v>6563634</v>
+        <v>6563544</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -3287,32 +3287,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128398996</v>
+        <v>128398408</v>
       </c>
       <c r="B26" t="n">
-        <v>92084</v>
+        <v>92774</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6031</v>
+        <v>1968</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687317</v>
+        <v>687462</v>
       </c>
       <c r="R26" t="n">
-        <v>6563634</v>
+        <v>6563544</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3388,32 +3388,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128398408</v>
+        <v>128398996</v>
       </c>
       <c r="B27" t="n">
-        <v>92774</v>
+        <v>92084</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1968</v>
+        <v>6031</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>687462</v>
+        <v>687317</v>
       </c>
       <c r="R27" t="n">
-        <v>6563544</v>
+        <v>6563634</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -3189,7 +3189,7 @@
         <v>128398377</v>
       </c>
       <c r="B25" t="n">
-        <v>92736</v>
+        <v>92748</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3287,32 +3287,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128398408</v>
+        <v>128398996</v>
       </c>
       <c r="B26" t="n">
-        <v>92774</v>
+        <v>92096</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1968</v>
+        <v>6031</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687462</v>
+        <v>687317</v>
       </c>
       <c r="R26" t="n">
-        <v>6563544</v>
+        <v>6563634</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3388,32 +3388,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128398996</v>
+        <v>128398408</v>
       </c>
       <c r="B27" t="n">
-        <v>92084</v>
+        <v>92786</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6031</v>
+        <v>1968</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>687317</v>
+        <v>687462</v>
       </c>
       <c r="R27" t="n">
-        <v>6563634</v>
+        <v>6563544</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3492,7 +3492,7 @@
         <v>128398269</v>
       </c>
       <c r="B28" t="n">
-        <v>92157</v>
+        <v>92169</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -3189,7 +3189,7 @@
         <v>128398377</v>
       </c>
       <c r="B25" t="n">
-        <v>92748</v>
+        <v>92750</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3287,32 +3287,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128398996</v>
+        <v>128398408</v>
       </c>
       <c r="B26" t="n">
-        <v>92096</v>
+        <v>92788</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6031</v>
+        <v>1968</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687317</v>
+        <v>687462</v>
       </c>
       <c r="R26" t="n">
-        <v>6563634</v>
+        <v>6563544</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3388,32 +3388,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128398408</v>
+        <v>128398996</v>
       </c>
       <c r="B27" t="n">
-        <v>92786</v>
+        <v>92098</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1968</v>
+        <v>6031</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>687462</v>
+        <v>687317</v>
       </c>
       <c r="R27" t="n">
-        <v>6563544</v>
+        <v>6563634</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3492,7 +3492,7 @@
         <v>128398269</v>
       </c>
       <c r="B28" t="n">
-        <v>92169</v>
+        <v>92171</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -3287,32 +3287,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128398408</v>
+        <v>128398996</v>
       </c>
       <c r="B26" t="n">
-        <v>92788</v>
+        <v>92098</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1968</v>
+        <v>6031</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687462</v>
+        <v>687317</v>
       </c>
       <c r="R26" t="n">
-        <v>6563544</v>
+        <v>6563634</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3388,32 +3388,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128398996</v>
+        <v>128398408</v>
       </c>
       <c r="B27" t="n">
-        <v>92098</v>
+        <v>92788</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6031</v>
+        <v>1968</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>687317</v>
+        <v>687462</v>
       </c>
       <c r="R27" t="n">
-        <v>6563634</v>
+        <v>6563544</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -3189,7 +3189,7 @@
         <v>128398377</v>
       </c>
       <c r="B25" t="n">
-        <v>92750</v>
+        <v>92751</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3287,32 +3287,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128398996</v>
+        <v>128398408</v>
       </c>
       <c r="B26" t="n">
-        <v>92098</v>
+        <v>92789</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6031</v>
+        <v>1968</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687317</v>
+        <v>687462</v>
       </c>
       <c r="R26" t="n">
-        <v>6563634</v>
+        <v>6563544</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3388,32 +3388,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128398408</v>
+        <v>128398996</v>
       </c>
       <c r="B27" t="n">
-        <v>92788</v>
+        <v>92099</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1968</v>
+        <v>6031</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>687462</v>
+        <v>687317</v>
       </c>
       <c r="R27" t="n">
-        <v>6563544</v>
+        <v>6563634</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3492,7 +3492,7 @@
         <v>128398269</v>
       </c>
       <c r="B28" t="n">
-        <v>92171</v>
+        <v>92172</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -3189,7 +3189,7 @@
         <v>128398377</v>
       </c>
       <c r="B25" t="n">
-        <v>92751</v>
+        <v>92778</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3287,32 +3287,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128398408</v>
+        <v>128398996</v>
       </c>
       <c r="B26" t="n">
-        <v>92789</v>
+        <v>92126</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1968</v>
+        <v>6031</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687462</v>
+        <v>687317</v>
       </c>
       <c r="R26" t="n">
-        <v>6563544</v>
+        <v>6563634</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3388,32 +3388,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128398996</v>
+        <v>128398408</v>
       </c>
       <c r="B27" t="n">
-        <v>92099</v>
+        <v>92816</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6031</v>
+        <v>1968</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>687317</v>
+        <v>687462</v>
       </c>
       <c r="R27" t="n">
-        <v>6563634</v>
+        <v>6563544</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3492,7 +3492,7 @@
         <v>128398269</v>
       </c>
       <c r="B28" t="n">
-        <v>92172</v>
+        <v>92199</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -3287,32 +3287,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128398996</v>
+        <v>128398408</v>
       </c>
       <c r="B26" t="n">
-        <v>92126</v>
+        <v>92816</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6031</v>
+        <v>1968</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687317</v>
+        <v>687462</v>
       </c>
       <c r="R26" t="n">
-        <v>6563634</v>
+        <v>6563544</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3388,32 +3388,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128398408</v>
+        <v>128398996</v>
       </c>
       <c r="B27" t="n">
-        <v>92816</v>
+        <v>92126</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1968</v>
+        <v>6031</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>687462</v>
+        <v>687317</v>
       </c>
       <c r="R27" t="n">
-        <v>6563544</v>
+        <v>6563634</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -3189,7 +3189,7 @@
         <v>128398377</v>
       </c>
       <c r="B25" t="n">
-        <v>92778</v>
+        <v>92788</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3287,32 +3287,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128398408</v>
+        <v>128398996</v>
       </c>
       <c r="B26" t="n">
-        <v>92816</v>
+        <v>92136</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1968</v>
+        <v>6031</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687462</v>
+        <v>687317</v>
       </c>
       <c r="R26" t="n">
-        <v>6563544</v>
+        <v>6563634</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3388,32 +3388,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128398996</v>
+        <v>128398408</v>
       </c>
       <c r="B27" t="n">
-        <v>92126</v>
+        <v>92828</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6031</v>
+        <v>1968</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>687317</v>
+        <v>687462</v>
       </c>
       <c r="R27" t="n">
-        <v>6563634</v>
+        <v>6563544</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3492,7 +3492,7 @@
         <v>128398269</v>
       </c>
       <c r="B28" t="n">
-        <v>92199</v>
+        <v>92209</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -3287,32 +3287,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128398996</v>
+        <v>128398408</v>
       </c>
       <c r="B26" t="n">
-        <v>92136</v>
+        <v>92828</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6031</v>
+        <v>1968</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687317</v>
+        <v>687462</v>
       </c>
       <c r="R26" t="n">
-        <v>6563634</v>
+        <v>6563544</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3388,32 +3388,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128398408</v>
+        <v>128398996</v>
       </c>
       <c r="B27" t="n">
-        <v>92828</v>
+        <v>92136</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1968</v>
+        <v>6031</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>687462</v>
+        <v>687317</v>
       </c>
       <c r="R27" t="n">
-        <v>6563544</v>
+        <v>6563634</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -3189,7 +3189,7 @@
         <v>128398377</v>
       </c>
       <c r="B25" t="n">
-        <v>92788</v>
+        <v>92792</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>128398408</v>
       </c>
       <c r="B26" t="n">
-        <v>92828</v>
+        <v>92832</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>128398996</v>
       </c>
       <c r="B27" t="n">
-        <v>92136</v>
+        <v>92140</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>128398269</v>
       </c>
       <c r="B28" t="n">
-        <v>92209</v>
+        <v>92213</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -3189,7 +3189,7 @@
         <v>128398377</v>
       </c>
       <c r="B25" t="n">
-        <v>92792</v>
+        <v>92797</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>128398408</v>
       </c>
       <c r="B26" t="n">
-        <v>92832</v>
+        <v>92837</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>128398996</v>
       </c>
       <c r="B27" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>128398269</v>
       </c>
       <c r="B28" t="n">
-        <v>92213</v>
+        <v>92218</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3583,6 +3583,515 @@
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129230567</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91738</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>687360</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6563644</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129230551</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91491</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>687338</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6563640</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129230833</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57883</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>687366</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6563649</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129230522</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91299</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>687359</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6563587</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129230467</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91526</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>687342</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6563554</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -3588,7 +3588,7 @@
         <v>129230567</v>
       </c>
       <c r="B29" t="n">
-        <v>91738</v>
+        <v>91745</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>129230551</v>
       </c>
       <c r="B30" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>129230833</v>
       </c>
       <c r="B31" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>129230522</v>
       </c>
       <c r="B32" t="n">
-        <v>91299</v>
+        <v>91305</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>129230467</v>
       </c>
       <c r="B33" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -3588,7 +3588,7 @@
         <v>129230567</v>
       </c>
       <c r="B29" t="n">
-        <v>91745</v>
+        <v>91752</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>129230551</v>
       </c>
       <c r="B30" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>129230522</v>
       </c>
       <c r="B32" t="n">
-        <v>91305</v>
+        <v>91312</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>129230467</v>
       </c>
       <c r="B33" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -3588,7 +3588,7 @@
         <v>129230567</v>
       </c>
       <c r="B29" t="n">
-        <v>91752</v>
+        <v>91754</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>129230551</v>
       </c>
       <c r="B30" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>129230833</v>
       </c>
       <c r="B31" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>129230522</v>
       </c>
       <c r="B32" t="n">
-        <v>91312</v>
+        <v>91314</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>129230467</v>
       </c>
       <c r="B33" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -3588,7 +3588,7 @@
         <v>129230567</v>
       </c>
       <c r="B29" t="n">
-        <v>91754</v>
+        <v>91763</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>129230551</v>
       </c>
       <c r="B30" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>129230522</v>
       </c>
       <c r="B32" t="n">
-        <v>91314</v>
+        <v>91313</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>129230467</v>
       </c>
       <c r="B33" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -3588,7 +3588,7 @@
         <v>129230567</v>
       </c>
       <c r="B29" t="n">
-        <v>91763</v>
+        <v>91764</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -3588,7 +3588,7 @@
         <v>129230567</v>
       </c>
       <c r="B29" t="n">
-        <v>91764</v>
+        <v>91767</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>129230551</v>
       </c>
       <c r="B30" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>129230522</v>
       </c>
       <c r="B32" t="n">
-        <v>91313</v>
+        <v>91316</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>129230467</v>
       </c>
       <c r="B33" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -3588,7 +3588,7 @@
         <v>129230567</v>
       </c>
       <c r="B29" t="n">
-        <v>91767</v>
+        <v>91769</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>129230551</v>
       </c>
       <c r="B30" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>129230522</v>
       </c>
       <c r="B32" t="n">
-        <v>91316</v>
+        <v>91318</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>129230467</v>
       </c>
       <c r="B33" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -3588,7 +3588,7 @@
         <v>129230567</v>
       </c>
       <c r="B29" t="n">
-        <v>91769</v>
+        <v>91773</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>129230551</v>
       </c>
       <c r="B30" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>129230522</v>
       </c>
       <c r="B32" t="n">
-        <v>91318</v>
+        <v>91322</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>129230467</v>
       </c>
       <c r="B33" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -3588,7 +3588,7 @@
         <v>129230567</v>
       </c>
       <c r="B29" t="n">
-        <v>91773</v>
+        <v>91774</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>129230551</v>
       </c>
       <c r="B30" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>129230522</v>
       </c>
       <c r="B32" t="n">
-        <v>91322</v>
+        <v>91323</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>129230467</v>
       </c>
       <c r="B33" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -3588,7 +3588,7 @@
         <v>129230567</v>
       </c>
       <c r="B29" t="n">
-        <v>91774</v>
+        <v>91777</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>129230551</v>
       </c>
       <c r="B30" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>129230522</v>
       </c>
       <c r="B32" t="n">
-        <v>91323</v>
+        <v>91326</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>129230467</v>
       </c>
       <c r="B33" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -3588,7 +3588,7 @@
         <v>129230567</v>
       </c>
       <c r="B29" t="n">
-        <v>91777</v>
+        <v>91805</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>129230551</v>
       </c>
       <c r="B30" t="n">
-        <v>91517</v>
+        <v>91545</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>129230833</v>
       </c>
       <c r="B31" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>129230522</v>
       </c>
       <c r="B32" t="n">
-        <v>91326</v>
+        <v>91354</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>129230467</v>
       </c>
       <c r="B33" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4092,6 +4092,111 @@
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129736793</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>687313</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6563541</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -4097,7 +4097,7 @@
         <v>129736793</v>
       </c>
       <c r="B34" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -4097,7 +4097,7 @@
         <v>129736793</v>
       </c>
       <c r="B34" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -4097,7 +4097,7 @@
         <v>129736793</v>
       </c>
       <c r="B34" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -4097,7 +4097,7 @@
         <v>129736793</v>
       </c>
       <c r="B34" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99519751</v>
+        <v>121859666</v>
       </c>
       <c r="B2" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>V Vargklova Mosse, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>687281.9339654517</v>
+        <v>687398</v>
       </c>
       <c r="R2" t="n">
-        <v>6563581.660678882</v>
+        <v>6563507</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,81 +764,63 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101523335</v>
+        <v>121859675</v>
       </c>
       <c r="B3" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>V Vargklova Mosse, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>687376.0987219027</v>
+        <v>687434</v>
       </c>
       <c r="R3" t="n">
-        <v>6563643.801713272</v>
+        <v>6563614</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,34 +871,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112319674</v>
+        <v>121859677</v>
       </c>
       <c r="B4" t="n">
-        <v>90849</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,37 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vargklova Mosse, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>687456</v>
+        <v>687329</v>
       </c>
       <c r="R4" t="n">
-        <v>6563544</v>
+        <v>6563566</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,12 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,34 +978,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121859682</v>
+        <v>101523335</v>
       </c>
       <c r="B5" t="n">
-        <v>97132</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,34 +1007,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221946</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>V Vargklova Mosse, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>687243</v>
+        <v>687376</v>
       </c>
       <c r="R5" t="n">
-        <v>6563593</v>
+        <v>6563644</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,22 +1073,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:52</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:52</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,33 +1087,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121859680</v>
+        <v>126004158</v>
       </c>
       <c r="B6" t="n">
-        <v>97135</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,34 +1117,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>210</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>687241</v>
+        <v>687335</v>
       </c>
       <c r="R6" t="n">
-        <v>6563587</v>
+        <v>6563581</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,22 +1183,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:58</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:58</t>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Mogna och uppsprickande kapslar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,33 +1202,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121859676</v>
+        <v>126004335</v>
       </c>
       <c r="B7" t="n">
-        <v>8436</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1263,34 +1232,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>210</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687355</v>
+        <v>687223</v>
       </c>
       <c r="R7" t="n">
-        <v>6563585</v>
+        <v>6563580</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,22 +1298,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:52</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:52</t>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Mogna och uppsprickande kapslar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,83 +1317,67 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121859683</v>
+        <v>128398950</v>
       </c>
       <c r="B8" t="n">
-        <v>97129</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687243</v>
+        <v>687323</v>
       </c>
       <c r="R8" t="n">
-        <v>6563593</v>
+        <v>6563661</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,22 +1404,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:52</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:52</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,33 +1418,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121859677</v>
+        <v>128399092</v>
       </c>
       <c r="B9" t="n">
-        <v>95722</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,34 +1448,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>687329</v>
+        <v>687300</v>
       </c>
       <c r="R9" t="n">
-        <v>6563566</v>
+        <v>6563657</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,22 +1505,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:12</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:12</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1580,56 +1519,56 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126004805</v>
+        <v>128398269</v>
       </c>
       <c r="B10" t="n">
-        <v>98278</v>
+        <v>92640</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>757</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1637,13 +1576,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>687448</v>
+        <v>687417</v>
       </c>
       <c r="R10" t="n">
         <v>6563548</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1667,12 +1606,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1700,38 +1639,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126004260</v>
+        <v>129230567</v>
       </c>
       <c r="B11" t="n">
-        <v>105396</v>
+        <v>92134</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>1106</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1739,10 +1677,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>687243</v>
+        <v>687360</v>
       </c>
       <c r="R11" t="n">
-        <v>6563585</v>
+        <v>6563644</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1769,12 +1707,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1802,38 +1740,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126004216</v>
+        <v>129230467</v>
       </c>
       <c r="B12" t="n">
-        <v>105396</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1841,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>687301</v>
+        <v>687342</v>
       </c>
       <c r="R12" t="n">
-        <v>6563579</v>
+        <v>6563554</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1871,12 +1808,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1904,46 +1841,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126004158</v>
+        <v>128398408</v>
       </c>
       <c r="B13" t="n">
-        <v>95810</v>
+        <v>93231</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>210</v>
+        <v>1968</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1951,10 +1879,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>687335</v>
+        <v>687462</v>
       </c>
       <c r="R13" t="n">
-        <v>6563581</v>
+        <v>6563544</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1981,17 +1909,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Mogna och uppsprickande kapslar.</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,52 +1942,51 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126004817</v>
+        <v>112492337</v>
       </c>
       <c r="B14" t="n">
-        <v>98278</v>
+        <v>92732</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>2014</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>V Vargklova mosse, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>687473</v>
+        <v>687375</v>
       </c>
       <c r="R14" t="n">
-        <v>6563539</v>
+        <v>6563689</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2088,12 +2010,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2023-10-02</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På asplåga.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2121,38 +2048,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126004295</v>
+        <v>128398912</v>
       </c>
       <c r="B15" t="n">
-        <v>105396</v>
+        <v>92732</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>2014</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2160,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>687291</v>
+        <v>687382</v>
       </c>
       <c r="R15" t="n">
-        <v>6563610</v>
+        <v>6563689</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2190,12 +2116,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2223,39 +2149,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126004787</v>
+        <v>128398945</v>
       </c>
       <c r="B16" t="n">
-        <v>58488</v>
+        <v>92732</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>208245</v>
+        <v>2014</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2263,10 +2187,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>687399</v>
+        <v>687323</v>
       </c>
       <c r="R16" t="n">
-        <v>6563564</v>
+        <v>6563661</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2293,12 +2217,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2326,38 +2250,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126004770</v>
+        <v>128399072</v>
       </c>
       <c r="B17" t="n">
-        <v>98278</v>
+        <v>92732</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>2014</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2365,10 +2288,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>687399</v>
+        <v>687300</v>
       </c>
       <c r="R17" t="n">
-        <v>6563564</v>
+        <v>6563657</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,12 +2318,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2428,10 +2351,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126004534</v>
+        <v>126079446</v>
       </c>
       <c r="B18" t="n">
-        <v>105396</v>
+        <v>96708</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2439,30 +2362,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>knoppbristning</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2471,10 +2390,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>687349</v>
+        <v>687416</v>
       </c>
       <c r="R18" t="n">
-        <v>6563661</v>
+        <v>6563568</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2534,10 +2453,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126079502</v>
+        <v>121859662</v>
       </c>
       <c r="B19" t="n">
-        <v>97239</v>
+        <v>96348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2545,41 +2464,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>2810</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>687453</v>
+        <v>687386</v>
       </c>
       <c r="R19" t="n">
-        <v>6563526</v>
+        <v>6563504</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2603,17 +2518,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt i kärret.</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2622,29 +2542,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126079446</v>
+        <v>129230522</v>
       </c>
       <c r="B20" t="n">
-        <v>95964</v>
+        <v>91680</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2652,27 +2571,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2180</v>
+        <v>3215</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2680,10 +2598,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>687416</v>
+        <v>687359</v>
       </c>
       <c r="R20" t="n">
-        <v>6563568</v>
+        <v>6563587</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2710,12 +2628,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2743,61 +2661,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126234839</v>
+        <v>112492249</v>
       </c>
       <c r="B21" t="n">
-        <v>98382</v>
+        <v>93189</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Vargklova mosse S om, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>687489</v>
+        <v>687493</v>
       </c>
       <c r="R21" t="n">
-        <v>6563516</v>
+        <v>6563530</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2824,12 +2729,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2845,69 +2750,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126212282</v>
+        <v>112319674</v>
       </c>
       <c r="B22" t="n">
-        <v>98361</v>
+        <v>93191</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Vargklova Mosse, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>687344</v>
+        <v>687456</v>
       </c>
       <c r="R22" t="n">
-        <v>6563653</v>
+        <v>6563544</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2934,12 +2830,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2967,61 +2863,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126234886</v>
+        <v>128398377</v>
       </c>
       <c r="B23" t="n">
-        <v>98382</v>
+        <v>93191</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>4362</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Vargklova mosse S om, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>687464</v>
+        <v>687458</v>
       </c>
       <c r="R23" t="n">
-        <v>6563531</v>
+        <v>6563552</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3048,12 +2931,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3069,68 +2952,63 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126419167</v>
+        <v>99519747</v>
       </c>
       <c r="B24" t="n">
-        <v>57817</v>
+        <v>91872</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>V Vargklova Mosse, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>687410</v>
+        <v>687419</v>
       </c>
       <c r="R24" t="n">
-        <v>6563618</v>
+        <v>6563508</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3154,12 +3032,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3168,6 +3046,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3186,32 +3065,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128398377</v>
+        <v>129230551</v>
       </c>
       <c r="B25" t="n">
-        <v>92797</v>
+        <v>91872</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4362</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3224,10 +3103,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>687458</v>
+        <v>687338</v>
       </c>
       <c r="R25" t="n">
-        <v>6563552</v>
+        <v>6563640</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3254,12 +3133,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3287,32 +3166,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128398408</v>
+        <v>129230845</v>
       </c>
       <c r="B26" t="n">
-        <v>92837</v>
+        <v>91872</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1968</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3325,10 +3204,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687462</v>
+        <v>687390</v>
       </c>
       <c r="R26" t="n">
-        <v>6563544</v>
+        <v>6563652</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3355,12 +3234,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3388,32 +3267,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128398996</v>
+        <v>129192906</v>
       </c>
       <c r="B27" t="n">
-        <v>92145</v>
+        <v>93223</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6031</v>
+        <v>5448</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3422,14 +3301,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>NO Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>687317</v>
+        <v>687478</v>
       </c>
       <c r="R27" t="n">
-        <v>6563634</v>
+        <v>6563566</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3456,12 +3335,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3489,27 +3368,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128398269</v>
+        <v>128398996</v>
       </c>
       <c r="B28" t="n">
-        <v>92220</v>
+        <v>92567</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>757</v>
+        <v>6031</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3522,10 +3406,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>687417</v>
+        <v>687317</v>
       </c>
       <c r="R28" t="n">
-        <v>6563548</v>
+        <v>6563634</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3585,37 +3469,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129230567</v>
+        <v>126419167</v>
       </c>
       <c r="B29" t="n">
-        <v>91805</v>
+        <v>58114</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1106</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3623,13 +3512,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>687360</v>
+        <v>687410</v>
       </c>
       <c r="R29" t="n">
-        <v>6563644</v>
+        <v>6563618</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3653,12 +3542,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3667,7 +3556,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3686,37 +3574,42 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129230551</v>
+        <v>129230833</v>
       </c>
       <c r="B30" t="n">
-        <v>91545</v>
+        <v>58114</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3724,13 +3617,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>687338</v>
+        <v>687366</v>
       </c>
       <c r="R30" t="n">
-        <v>6563640</v>
+        <v>6563649</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3768,7 +3661,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3787,10 +3679,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129230833</v>
+        <v>129736793</v>
       </c>
       <c r="B31" t="n">
-        <v>57890</v>
+        <v>58114</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3830,13 +3722,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>687366</v>
+        <v>687313</v>
       </c>
       <c r="R31" t="n">
-        <v>6563649</v>
+        <v>6563541</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3860,12 +3752,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3892,10 +3784,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129230522</v>
+        <v>121859676</v>
       </c>
       <c r="B32" t="n">
-        <v>91354</v>
+        <v>8455</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3903,37 +3795,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3215</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>687359</v>
+        <v>687355</v>
       </c>
       <c r="R32" t="n">
-        <v>6563587</v>
+        <v>6563585</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3960,12 +3849,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3974,56 +3873,72 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129230467</v>
+        <v>126004787</v>
       </c>
       <c r="B33" t="n">
-        <v>91581</v>
+        <v>58790</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>208245</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4031,10 +3946,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>687342</v>
+        <v>687399</v>
       </c>
       <c r="R33" t="n">
-        <v>6563554</v>
+        <v>6563564</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4061,12 +3976,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4094,42 +4009,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129736793</v>
+        <v>126004064</v>
       </c>
       <c r="B34" t="n">
-        <v>57899</v>
+        <v>99035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4137,13 +4048,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>687313</v>
+        <v>687237</v>
       </c>
       <c r="R34" t="n">
-        <v>6563541</v>
+        <v>6563533</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4167,12 +4078,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4181,6 +4092,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4196,6 +4108,2234 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126004770</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>687399</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6563564</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126004805</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>687448</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6563548</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126004817</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>687473</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6563539</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126212282</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>687344</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6563653</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>99519751</v>
+      </c>
+      <c r="B39" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>V Vargklova Mosse, Srm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>687282</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6563582</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2022-03-28</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2022-03-28</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>126004216</v>
+      </c>
+      <c r="B40" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>687301</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6563579</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>126004260</v>
+      </c>
+      <c r="B41" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>687243</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6563585</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>126004295</v>
+      </c>
+      <c r="B42" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>687291</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6563610</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>126004534</v>
+      </c>
+      <c r="B43" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>knoppbristning</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>687349</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6563661</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>78194577</v>
+      </c>
+      <c r="B44" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Sävkärrs mosse SO/NP-gränsen, Srm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>687235</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6563600</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2019-06-02</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2019-06-02</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ett flertal fortf. vid god vigör men många döda och vissna</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>111689384</v>
+      </c>
+      <c r="B45" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>S Vargklova mosse, Srm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>687532</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6563517</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2023-08-21</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2023-08-21</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>121859680</v>
+      </c>
+      <c r="B46" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>687241</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6563587</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>121859681</v>
+      </c>
+      <c r="B47" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>687245</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6563595</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>121859668</v>
+      </c>
+      <c r="B48" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>687531</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6563515</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>121859678</v>
+      </c>
+      <c r="B49" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>687239</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6563531</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Mycket rikligt.</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>121859679</v>
+      </c>
+      <c r="B50" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>687220</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6563556</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>121859683</v>
+      </c>
+      <c r="B51" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>687243</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6563593</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>126079502</v>
+      </c>
+      <c r="B52" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>687453</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6563526</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rikligt i kärret.</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>121859682</v>
+      </c>
+      <c r="B53" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>687243</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6563593</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>126234839</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Vargklova mosse S om, Srm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>687489</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6563516</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Ulf Johansson, Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>126234886</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Vargklova mosse S om, Srm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>687464</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6563531</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Ulf Johansson, Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6337,6 +6337,117 @@
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>134487957</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>687245</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6563523</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>11 i blom samt flera plantor med endast blad. Kan ha varit fler.</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -6422,7 +6422,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>11 i blom samt flera plantor med endast blad. Kan ha varit fler.</t>
+          <t>11 i blom samt flera plantor med endast blad.</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AZ56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859666</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859675</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859677</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,6 +1123,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101523335</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1218,6 +1243,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126004158</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1333,6 +1363,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126004335</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1434,6 +1469,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128398950</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1535,6 +1575,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128399092</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1636,6 +1681,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128398269</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1737,6 +1787,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230567</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1838,6 +1893,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230467</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1939,6 +1999,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128398408</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2045,6 +2110,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112492337</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2146,6 +2216,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128398912</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2247,6 +2322,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128398945</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2348,6 +2428,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128399072</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2450,6 +2535,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126079446</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2557,6 +2647,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859662</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2658,6 +2753,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230522</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2759,6 +2859,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112492249</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2860,6 +2965,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112319674</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2961,6 +3071,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128398377</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3062,6 +3177,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99519747</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3163,6 +3283,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230551</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3264,6 +3389,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230845</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3365,6 +3495,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129192906</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3466,6 +3601,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128398996</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3571,6 +3711,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126419167</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3676,6 +3821,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230833</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3781,6 +3931,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129736793</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3903,6 +4058,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859676</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4006,6 +4166,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126004787</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4108,6 +4273,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126004064</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4210,6 +4380,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126004770</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4312,6 +4487,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126004805</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4414,6 +4594,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126004817</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4524,6 +4709,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126212282</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4626,6 +4816,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99519751</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4728,6 +4923,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126004216</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4830,6 +5030,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126004260</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4932,6 +5137,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126004295</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5038,6 +5248,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126004534</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5145,6 +5360,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78194577</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5247,6 +5467,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111689384</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5354,6 +5579,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859680</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5461,6 +5691,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859681</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5568,6 +5803,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859668</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5680,6 +5920,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859678</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5787,6 +6032,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859679</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5894,6 +6144,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859683</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6001,6 +6256,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126079502</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6108,6 +6368,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859682</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6222,6 +6487,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126234839</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6336,6 +6606,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126234886</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6447,8 +6722,70 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134487957</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ56"/>
+  <dimension ref="A1:AZ57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3079,32 +3079,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>99519747</v>
+        <v>135827336</v>
       </c>
       <c r="B24" t="n">
-        <v>91872</v>
+        <v>93345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3113,14 +3113,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>V Vargklova Mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>687419</v>
+        <v>687344</v>
       </c>
       <c r="R24" t="n">
-        <v>6563508</v>
+        <v>6563552</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3147,12 +3147,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3179,13 +3179,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99519747</t>
+          <t>https://artportalen.se/Sighting/135827336</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129230551</v>
+        <v>99519747</v>
       </c>
       <c r="B25" t="n">
         <v>91872</v>
@@ -3219,14 +3219,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>V Vargklova Mosse, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>687338</v>
+        <v>687419</v>
       </c>
       <c r="R25" t="n">
-        <v>6563640</v>
+        <v>6563508</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3253,12 +3253,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3285,13 +3285,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129230551</t>
+          <t>https://artportalen.se/Sighting/99519747</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129230845</v>
+        <v>129230551</v>
       </c>
       <c r="B26" t="n">
         <v>91872</v>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687390</v>
+        <v>687338</v>
       </c>
       <c r="R26" t="n">
-        <v>6563652</v>
+        <v>6563640</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3391,38 +3391,38 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129230845</t>
+          <t>https://artportalen.se/Sighting/129230551</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129192906</v>
+        <v>129230845</v>
       </c>
       <c r="B27" t="n">
-        <v>93223</v>
+        <v>91872</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5448</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3431,14 +3431,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>NO Norrbytorp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>687478</v>
+        <v>687390</v>
       </c>
       <c r="R27" t="n">
-        <v>6563566</v>
+        <v>6563652</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3465,12 +3465,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3497,38 +3497,38 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129192906</t>
+          <t>https://artportalen.se/Sighting/129230845</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128398996</v>
+        <v>129192906</v>
       </c>
       <c r="B28" t="n">
-        <v>92567</v>
+        <v>93223</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6031</v>
+        <v>5448</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3537,14 +3537,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>NO Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>687317</v>
+        <v>687478</v>
       </c>
       <c r="R28" t="n">
-        <v>6563634</v>
+        <v>6563566</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3603,48 +3603,43 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128398996</t>
+          <t>https://artportalen.se/Sighting/129192906</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126419167</v>
+        <v>128398996</v>
       </c>
       <c r="B29" t="n">
-        <v>58114</v>
+        <v>92567</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6031</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3652,13 +3647,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>687410</v>
+        <v>687317</v>
       </c>
       <c r="R29" t="n">
-        <v>6563618</v>
+        <v>6563634</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3682,12 +3677,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3696,6 +3691,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3713,13 +3709,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126419167</t>
+          <t>https://artportalen.se/Sighting/128398996</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129230833</v>
+        <v>126419167</v>
       </c>
       <c r="B30" t="n">
         <v>58114</v>
@@ -3762,10 +3758,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>687366</v>
+        <v>687410</v>
       </c>
       <c r="R30" t="n">
-        <v>6563649</v>
+        <v>6563618</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3792,12 +3788,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3823,13 +3819,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129230833</t>
+          <t>https://artportalen.se/Sighting/126419167</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129736793</v>
+        <v>129230833</v>
       </c>
       <c r="B31" t="n">
         <v>58114</v>
@@ -3872,13 +3868,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>687313</v>
+        <v>687366</v>
       </c>
       <c r="R31" t="n">
-        <v>6563541</v>
+        <v>6563649</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3902,12 +3898,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3933,51 +3929,59 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129736793</t>
+          <t>https://artportalen.se/Sighting/129230833</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121859676</v>
+        <v>129736793</v>
       </c>
       <c r="B32" t="n">
-        <v>8455</v>
+        <v>58114</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>687355</v>
+        <v>687313</v>
       </c>
       <c r="R32" t="n">
-        <v>6563585</v>
+        <v>6563541</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4004,22 +4008,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>12:52</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>12:52</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4030,46 +4024,31 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859676</t>
+          <t>https://artportalen.se/Sighting/129736793</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126004787</v>
+        <v>121859676</v>
       </c>
       <c r="B33" t="n">
-        <v>58790</v>
+        <v>8455</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4077,39 +4056,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>208245</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>687399</v>
+        <v>687355</v>
       </c>
       <c r="R33" t="n">
-        <v>6563564</v>
+        <v>6563585</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4136,12 +4110,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4150,34 +4134,48 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126004787</t>
+          <t>https://artportalen.se/Sighting/121859676</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126004064</v>
+        <v>126004787</v>
       </c>
       <c r="B34" t="n">
-        <v>99035</v>
+        <v>58790</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4185,27 +4183,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219790</v>
+        <v>208245</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4213,13 +4212,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>687237</v>
+        <v>687399</v>
       </c>
       <c r="R34" t="n">
-        <v>6563533</v>
+        <v>6563564</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4275,13 +4274,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126004064</t>
+          <t>https://artportalen.se/Sighting/126004787</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126004770</v>
+        <v>126004064</v>
       </c>
       <c r="B35" t="n">
         <v>99035</v>
@@ -4320,13 +4319,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>687399</v>
+        <v>687237</v>
       </c>
       <c r="R35" t="n">
-        <v>6563564</v>
+        <v>6563533</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4382,13 +4381,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126004770</t>
+          <t>https://artportalen.se/Sighting/126004064</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126004805</v>
+        <v>126004770</v>
       </c>
       <c r="B36" t="n">
         <v>99035</v>
@@ -4427,13 +4426,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>687448</v>
+        <v>687399</v>
       </c>
       <c r="R36" t="n">
-        <v>6563548</v>
+        <v>6563564</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4489,13 +4488,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126004805</t>
+          <t>https://artportalen.se/Sighting/126004770</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126004817</v>
+        <v>126004805</v>
       </c>
       <c r="B37" t="n">
         <v>99035</v>
@@ -4534,10 +4533,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>687473</v>
+        <v>687448</v>
       </c>
       <c r="R37" t="n">
-        <v>6563539</v>
+        <v>6563548</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4596,50 +4595,42 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126004817</t>
+          <t>https://artportalen.se/Sighting/126004805</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126212282</v>
+        <v>126004817</v>
       </c>
       <c r="B38" t="n">
-        <v>99118</v>
+        <v>99035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -4649,13 +4640,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>687344</v>
+        <v>687473</v>
       </c>
       <c r="R38" t="n">
-        <v>6563653</v>
+        <v>6563539</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4679,12 +4670,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4711,55 +4702,63 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126212282</t>
+          <t>https://artportalen.se/Sighting/126004817</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>99519751</v>
+        <v>126212282</v>
       </c>
       <c r="B39" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>V Vargklova Mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>687282</v>
+        <v>687344</v>
       </c>
       <c r="R39" t="n">
-        <v>6563582</v>
+        <v>6563653</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4786,12 +4785,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4818,13 +4817,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99519751</t>
+          <t>https://artportalen.se/Sighting/126212282</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126004216</v>
+        <v>99519751</v>
       </c>
       <c r="B40" t="n">
         <v>106244</v>
@@ -4859,14 +4858,14 @@
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>V Vargklova Mosse, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>687301</v>
+        <v>687282</v>
       </c>
       <c r="R40" t="n">
-        <v>6563579</v>
+        <v>6563582</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4893,12 +4892,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4925,13 +4924,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126004216</t>
+          <t>https://artportalen.se/Sighting/99519751</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126004260</v>
+        <v>126004216</v>
       </c>
       <c r="B41" t="n">
         <v>106244</v>
@@ -4970,10 +4969,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>687243</v>
+        <v>687301</v>
       </c>
       <c r="R41" t="n">
-        <v>6563585</v>
+        <v>6563579</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5032,13 +5031,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126004260</t>
+          <t>https://artportalen.se/Sighting/126004216</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126004295</v>
+        <v>126004260</v>
       </c>
       <c r="B42" t="n">
         <v>106244</v>
@@ -5077,10 +5076,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>687291</v>
+        <v>687243</v>
       </c>
       <c r="R42" t="n">
-        <v>6563610</v>
+        <v>6563585</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5139,13 +5138,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126004295</t>
+          <t>https://artportalen.se/Sighting/126004260</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126004534</v>
+        <v>126004295</v>
       </c>
       <c r="B43" t="n">
         <v>106244</v>
@@ -5175,11 +5174,7 @@
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>knoppbristning</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
@@ -5188,10 +5183,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>687349</v>
+        <v>687291</v>
       </c>
       <c r="R43" t="n">
-        <v>6563661</v>
+        <v>6563610</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5250,16 +5245,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126004534</t>
+          <t>https://artportalen.se/Sighting/126004295</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>78194577</v>
+        <v>126004534</v>
       </c>
       <c r="B44" t="n">
-        <v>97989</v>
+        <v>106244</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5267,41 +5262,45 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>knoppbristning</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sävkärrs mosse SO/NP-gränsen, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>687235</v>
+        <v>687349</v>
       </c>
       <c r="R44" t="n">
-        <v>6563600</v>
+        <v>6563661</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5325,17 +5324,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2019-06-02</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2019-06-02</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ett flertal fortf. vid god vigör men många döda och vissna</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5351,24 +5345,24 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78194577</t>
+          <t>https://artportalen.se/Sighting/126004534</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>111689384</v>
+        <v>78194577</v>
       </c>
       <c r="B45" t="n">
         <v>97989</v>
@@ -5403,17 +5397,17 @@
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>S Vargklova mosse, Srm</t>
+          <t>Sävkärrs mosse SO/NP-gränsen, Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>687532</v>
+        <v>687235</v>
       </c>
       <c r="R45" t="n">
-        <v>6563517</v>
+        <v>6563600</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5437,12 +5431,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2019-06-02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2019-06-02</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ett flertal fortf. vid god vigör men många döda och vissna</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5458,24 +5457,24 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111689384</t>
+          <t>https://artportalen.se/Sighting/78194577</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121859680</v>
+        <v>111689384</v>
       </c>
       <c r="B46" t="n">
         <v>97989</v>
@@ -5504,16 +5503,20 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>S Vargklova mosse, Srm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>687241</v>
+        <v>687532</v>
       </c>
       <c r="R46" t="n">
-        <v>6563587</v>
+        <v>6563517</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5540,22 +5543,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>11:58</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>11:58</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5564,30 +5557,31 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859680</t>
+          <t>https://artportalen.se/Sighting/111689384</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121859681</v>
+        <v>121859680</v>
       </c>
       <c r="B47" t="n">
         <v>97989</v>
@@ -5622,10 +5616,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>687245</v>
+        <v>687241</v>
       </c>
       <c r="R47" t="n">
-        <v>6563595</v>
+        <v>6563587</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5657,7 +5651,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5667,7 +5661,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5693,16 +5687,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859681</t>
+          <t>https://artportalen.se/Sighting/121859680</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121859668</v>
+        <v>121859681</v>
       </c>
       <c r="B48" t="n">
-        <v>97983</v>
+        <v>97989</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5710,16 +5704,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5734,10 +5728,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>687531</v>
+        <v>687245</v>
       </c>
       <c r="R48" t="n">
-        <v>6563515</v>
+        <v>6563595</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5769,7 +5763,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5779,7 +5773,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5805,13 +5799,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859668</t>
+          <t>https://artportalen.se/Sighting/121859681</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121859678</v>
+        <v>121859668</v>
       </c>
       <c r="B49" t="n">
         <v>97983</v>
@@ -5846,10 +5840,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>687239</v>
+        <v>687531</v>
       </c>
       <c r="R49" t="n">
-        <v>6563531</v>
+        <v>6563515</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5881,7 +5875,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5891,12 +5885,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Mycket rikligt.</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5922,13 +5911,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859678</t>
+          <t>https://artportalen.se/Sighting/121859668</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121859679</v>
+        <v>121859678</v>
       </c>
       <c r="B50" t="n">
         <v>97983</v>
@@ -5963,10 +5952,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>687220</v>
+        <v>687239</v>
       </c>
       <c r="R50" t="n">
-        <v>6563556</v>
+        <v>6563531</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5998,7 +5987,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6008,7 +5997,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Mycket rikligt.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6034,13 +6028,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859679</t>
+          <t>https://artportalen.se/Sighting/121859678</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121859683</v>
+        <v>121859679</v>
       </c>
       <c r="B51" t="n">
         <v>97983</v>
@@ -6075,10 +6069,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>687243</v>
+        <v>687220</v>
       </c>
       <c r="R51" t="n">
-        <v>6563593</v>
+        <v>6563556</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6110,7 +6104,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6120,7 +6114,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6146,13 +6140,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859683</t>
+          <t>https://artportalen.se/Sighting/121859679</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126079502</v>
+        <v>121859683</v>
       </c>
       <c r="B52" t="n">
         <v>97983</v>
@@ -6181,23 +6175,19 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>687453</v>
+        <v>687243</v>
       </c>
       <c r="R52" t="n">
-        <v>6563526</v>
+        <v>6563593</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6221,17 +6211,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Rikligt i kärret.</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6240,34 +6235,33 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126079502</t>
+          <t>https://artportalen.se/Sighting/121859683</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121859682</v>
+        <v>126079502</v>
       </c>
       <c r="B53" t="n">
-        <v>97986</v>
+        <v>97983</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6275,16 +6269,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6293,19 +6287,23 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>687243</v>
+        <v>687453</v>
       </c>
       <c r="R53" t="n">
-        <v>6563593</v>
+        <v>6563526</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6329,22 +6327,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>11:52</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>11:52</t>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Rikligt i kärret.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6353,33 +6346,34 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859682</t>
+          <t>https://artportalen.se/Sighting/126079502</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126234839</v>
+        <v>121859682</v>
       </c>
       <c r="B54" t="n">
-        <v>99140</v>
+        <v>97986</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6387,50 +6381,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221952</v>
+        <v>221946</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Vargklova mosse S om, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>687489</v>
+        <v>687243</v>
       </c>
       <c r="R54" t="n">
-        <v>6563516</v>
+        <v>6563593</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6457,12 +6435,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6471,31 +6459,30 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234839</t>
+          <t>https://artportalen.se/Sighting/121859682</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126234886</v>
+        <v>126234839</v>
       </c>
       <c r="B55" t="n">
         <v>99140</v>
@@ -6535,7 +6522,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
@@ -6546,10 +6533,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>687464</v>
+        <v>687489</v>
       </c>
       <c r="R55" t="n">
-        <v>6563531</v>
+        <v>6563516</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6608,16 +6595,16 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234886</t>
+          <t>https://artportalen.se/Sighting/126234839</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134487957</v>
+        <v>126234886</v>
       </c>
       <c r="B56" t="n">
-        <v>99217</v>
+        <v>99140</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6642,8 +6629,16 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -6653,17 +6648,17 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Vargklova mosse S om, Srm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>687245</v>
+        <v>687464</v>
       </c>
       <c r="R56" t="n">
-        <v>6563523</v>
+        <v>6563531</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6687,17 +6682,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>11 i blom samt flera plantor med endast blad.</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6713,16 +6703,132 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126234886</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>134487957</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>687245</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6563523</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>11 i blom samt flera plantor med endast blad.</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134487957</t>
         </is>
@@ -6785,6 +6891,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -3082,7 +3082,7 @@
         <v>135827336</v>
       </c>
       <c r="B24" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -3082,7 +3082,7 @@
         <v>135827336</v>
       </c>
       <c r="B24" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ57"/>
+  <dimension ref="A1:AZ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1371,37 +1371,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128398950</v>
+        <v>136159865</v>
       </c>
       <c r="B8" t="n">
-        <v>92699</v>
+        <v>96725</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>366</v>
+        <v>210</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1409,10 +1418,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687323</v>
+        <v>687302</v>
       </c>
       <c r="R8" t="n">
-        <v>6563661</v>
+        <v>6563640</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,12 +1448,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Uppsprucken kapsel.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,13 +1485,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128398950</t>
+          <t>https://artportalen.se/Sighting/136159865</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128399092</v>
+        <v>128398950</v>
       </c>
       <c r="B9" t="n">
         <v>92699</v>
@@ -1515,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>687300</v>
+        <v>687323</v>
       </c>
       <c r="R9" t="n">
-        <v>6563657</v>
+        <v>6563661</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1577,16 +1591,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128399092</t>
+          <t>https://artportalen.se/Sighting/128398950</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128398269</v>
+        <v>128399092</v>
       </c>
       <c r="B10" t="n">
-        <v>92640</v>
+        <v>92699</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1594,21 +1608,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>757</v>
+        <v>366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1621,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>687417</v>
+        <v>687300</v>
       </c>
       <c r="R10" t="n">
-        <v>6563548</v>
+        <v>6563657</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,16 +1697,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128398269</t>
+          <t>https://artportalen.se/Sighting/128399092</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129230567</v>
+        <v>128398269</v>
       </c>
       <c r="B11" t="n">
-        <v>92134</v>
+        <v>92640</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1700,21 +1714,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1106</v>
+        <v>757</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1727,10 +1741,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>687360</v>
+        <v>687417</v>
       </c>
       <c r="R11" t="n">
-        <v>6563644</v>
+        <v>6563548</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1757,12 +1771,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1789,16 +1803,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129230567</t>
+          <t>https://artportalen.se/Sighting/128398269</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129230467</v>
+        <v>129230567</v>
       </c>
       <c r="B12" t="n">
-        <v>91909</v>
+        <v>92134</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,21 +1820,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1106</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1833,10 +1847,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>687342</v>
+        <v>687360</v>
       </c>
       <c r="R12" t="n">
-        <v>6563554</v>
+        <v>6563644</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,16 +1909,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129230467</t>
+          <t>https://artportalen.se/Sighting/129230567</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128398408</v>
+        <v>129230467</v>
       </c>
       <c r="B13" t="n">
-        <v>93231</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1912,21 +1926,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1968</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1939,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>687462</v>
+        <v>687342</v>
       </c>
       <c r="R13" t="n">
-        <v>6563544</v>
+        <v>6563554</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1969,12 +1983,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2001,16 +2015,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128398408</t>
+          <t>https://artportalen.se/Sighting/129230467</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112492337</v>
+        <v>128398408</v>
       </c>
       <c r="B14" t="n">
-        <v>92732</v>
+        <v>93231</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2018,21 +2032,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2014</v>
+        <v>1968</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2041,14 +2055,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>V Vargklova mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>687375</v>
+        <v>687462</v>
       </c>
       <c r="R14" t="n">
-        <v>6563689</v>
+        <v>6563544</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2075,17 +2089,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På asplåga.</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2112,13 +2121,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112492337</t>
+          <t>https://artportalen.se/Sighting/128398408</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128398912</v>
+        <v>112492337</v>
       </c>
       <c r="B15" t="n">
         <v>92732</v>
@@ -2152,11 +2161,11 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>V Vargklova mosse, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>687382</v>
+        <v>687375</v>
       </c>
       <c r="R15" t="n">
         <v>6563689</v>
@@ -2186,12 +2195,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2023-10-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På asplåga.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2218,13 +2232,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128398912</t>
+          <t>https://artportalen.se/Sighting/112492337</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128398945</v>
+        <v>128398912</v>
       </c>
       <c r="B16" t="n">
         <v>92732</v>
@@ -2262,10 +2276,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>687323</v>
+        <v>687382</v>
       </c>
       <c r="R16" t="n">
-        <v>6563661</v>
+        <v>6563689</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2324,13 +2338,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128398945</t>
+          <t>https://artportalen.se/Sighting/128398912</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128399072</v>
+        <v>128398945</v>
       </c>
       <c r="B17" t="n">
         <v>92732</v>
@@ -2368,10 +2382,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>687300</v>
+        <v>687323</v>
       </c>
       <c r="R17" t="n">
-        <v>6563657</v>
+        <v>6563661</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2430,44 +2444,43 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128399072</t>
+          <t>https://artportalen.se/Sighting/128398945</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126079446</v>
+        <v>128399072</v>
       </c>
       <c r="B18" t="n">
-        <v>96708</v>
+        <v>92732</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>2014</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2475,10 +2488,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>687416</v>
+        <v>687300</v>
       </c>
       <c r="R18" t="n">
-        <v>6563568</v>
+        <v>6563657</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2505,12 +2518,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2537,16 +2550,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126079446</t>
+          <t>https://artportalen.se/Sighting/128399072</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121859662</v>
+        <v>126079446</v>
       </c>
       <c r="B19" t="n">
-        <v>96348</v>
+        <v>96708</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2554,34 +2567,38 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2810</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>687386</v>
+        <v>687416</v>
       </c>
       <c r="R19" t="n">
-        <v>6563504</v>
+        <v>6563568</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2608,22 +2625,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:24</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:24</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2632,33 +2639,34 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859662</t>
+          <t>https://artportalen.se/Sighting/126079446</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129230522</v>
+        <v>121859662</v>
       </c>
       <c r="B20" t="n">
-        <v>91680</v>
+        <v>96348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2666,37 +2674,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3215</v>
+        <v>2810</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>687359</v>
+        <v>687386</v>
       </c>
       <c r="R20" t="n">
-        <v>6563587</v>
+        <v>6563504</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2723,12 +2728,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2737,56 +2752,55 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129230522</t>
+          <t>https://artportalen.se/Sighting/121859662</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112492249</v>
+        <v>129230522</v>
       </c>
       <c r="B21" t="n">
-        <v>93189</v>
+        <v>91680</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4361</v>
+        <v>3215</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2799,10 +2813,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>687493</v>
+        <v>687359</v>
       </c>
       <c r="R21" t="n">
-        <v>6563530</v>
+        <v>6563587</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2829,12 +2843,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2861,16 +2875,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112492249</t>
+          <t>https://artportalen.se/Sighting/129230522</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112319674</v>
+        <v>112492249</v>
       </c>
       <c r="B22" t="n">
-        <v>93191</v>
+        <v>93189</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2878,21 +2892,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2901,14 +2915,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vargklova Mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>687456</v>
+        <v>687493</v>
       </c>
       <c r="R22" t="n">
-        <v>6563544</v>
+        <v>6563530</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2935,12 +2949,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2967,13 +2981,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112319674</t>
+          <t>https://artportalen.se/Sighting/112492249</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128398377</v>
+        <v>112319674</v>
       </c>
       <c r="B23" t="n">
         <v>93191</v>
@@ -3007,14 +3021,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Vargklova Mosse, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>687458</v>
+        <v>687456</v>
       </c>
       <c r="R23" t="n">
-        <v>6563552</v>
+        <v>6563544</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3041,12 +3055,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3073,16 +3087,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128398377</t>
+          <t>https://artportalen.se/Sighting/112319674</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135827336</v>
+        <v>128398377</v>
       </c>
       <c r="B24" t="n">
-        <v>93362</v>
+        <v>93191</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3090,21 +3104,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3117,7 +3131,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>687344</v>
+        <v>687458</v>
       </c>
       <c r="R24" t="n">
         <v>6563552</v>
@@ -3147,12 +3161,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3179,38 +3193,38 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135827336</t>
+          <t>https://artportalen.se/Sighting/128398377</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>99519747</v>
+        <v>135827336</v>
       </c>
       <c r="B25" t="n">
-        <v>91872</v>
+        <v>93362</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3219,14 +3233,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>V Vargklova Mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>687419</v>
+        <v>687344</v>
       </c>
       <c r="R25" t="n">
-        <v>6563508</v>
+        <v>6563552</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3253,12 +3267,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3285,13 +3299,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99519747</t>
+          <t>https://artportalen.se/Sighting/135827336</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129230551</v>
+        <v>99519747</v>
       </c>
       <c r="B26" t="n">
         <v>91872</v>
@@ -3325,14 +3339,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>V Vargklova Mosse, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687338</v>
+        <v>687419</v>
       </c>
       <c r="R26" t="n">
-        <v>6563640</v>
+        <v>6563508</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3359,12 +3373,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3391,13 +3405,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129230551</t>
+          <t>https://artportalen.se/Sighting/99519747</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129230845</v>
+        <v>129230551</v>
       </c>
       <c r="B27" t="n">
         <v>91872</v>
@@ -3435,10 +3449,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>687390</v>
+        <v>687338</v>
       </c>
       <c r="R27" t="n">
-        <v>6563652</v>
+        <v>6563640</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3497,38 +3511,38 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129230845</t>
+          <t>https://artportalen.se/Sighting/129230551</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129192906</v>
+        <v>129230845</v>
       </c>
       <c r="B28" t="n">
-        <v>93223</v>
+        <v>91872</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5448</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3537,14 +3551,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>NO Norrbytorp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>687478</v>
+        <v>687390</v>
       </c>
       <c r="R28" t="n">
-        <v>6563566</v>
+        <v>6563652</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3571,12 +3585,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3603,38 +3617,38 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129192906</t>
+          <t>https://artportalen.se/Sighting/129230845</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128398996</v>
+        <v>129192906</v>
       </c>
       <c r="B29" t="n">
-        <v>92567</v>
+        <v>93223</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6031</v>
+        <v>5448</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3643,14 +3657,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>NO Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>687317</v>
+        <v>687478</v>
       </c>
       <c r="R29" t="n">
-        <v>6563634</v>
+        <v>6563566</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3677,12 +3691,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3709,48 +3723,43 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128398996</t>
+          <t>https://artportalen.se/Sighting/129192906</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126419167</v>
+        <v>128398996</v>
       </c>
       <c r="B30" t="n">
-        <v>58114</v>
+        <v>92567</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>6031</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3758,13 +3767,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>687410</v>
+        <v>687317</v>
       </c>
       <c r="R30" t="n">
-        <v>6563618</v>
+        <v>6563634</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3788,12 +3797,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3802,6 +3811,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3819,13 +3829,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126419167</t>
+          <t>https://artportalen.se/Sighting/128398996</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129230833</v>
+        <v>126419167</v>
       </c>
       <c r="B31" t="n">
         <v>58114</v>
@@ -3868,10 +3878,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>687366</v>
+        <v>687410</v>
       </c>
       <c r="R31" t="n">
-        <v>6563649</v>
+        <v>6563618</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3898,12 +3908,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3929,13 +3939,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129230833</t>
+          <t>https://artportalen.se/Sighting/126419167</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129736793</v>
+        <v>129230833</v>
       </c>
       <c r="B32" t="n">
         <v>58114</v>
@@ -3978,13 +3988,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>687313</v>
+        <v>687366</v>
       </c>
       <c r="R32" t="n">
-        <v>6563541</v>
+        <v>6563649</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4008,12 +4018,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4039,51 +4049,59 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129736793</t>
+          <t>https://artportalen.se/Sighting/129230833</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121859676</v>
+        <v>129736793</v>
       </c>
       <c r="B33" t="n">
-        <v>8455</v>
+        <v>58114</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>687355</v>
+        <v>687313</v>
       </c>
       <c r="R33" t="n">
-        <v>6563585</v>
+        <v>6563541</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4110,22 +4128,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>12:52</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>12:52</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4136,46 +4144,31 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859676</t>
+          <t>https://artportalen.se/Sighting/129736793</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126004787</v>
+        <v>121859676</v>
       </c>
       <c r="B34" t="n">
-        <v>58790</v>
+        <v>8455</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4183,39 +4176,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>208245</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>687399</v>
+        <v>687355</v>
       </c>
       <c r="R34" t="n">
-        <v>6563564</v>
+        <v>6563585</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4242,12 +4230,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4256,34 +4254,48 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126004787</t>
+          <t>https://artportalen.se/Sighting/121859676</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126004064</v>
+        <v>126004787</v>
       </c>
       <c r="B35" t="n">
-        <v>99035</v>
+        <v>58790</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4291,27 +4303,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219790</v>
+        <v>208245</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4319,13 +4332,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>687237</v>
+        <v>687399</v>
       </c>
       <c r="R35" t="n">
-        <v>6563533</v>
+        <v>6563564</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4381,13 +4394,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126004064</t>
+          <t>https://artportalen.se/Sighting/126004787</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126004770</v>
+        <v>126004064</v>
       </c>
       <c r="B36" t="n">
         <v>99035</v>
@@ -4426,13 +4439,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>687399</v>
+        <v>687237</v>
       </c>
       <c r="R36" t="n">
-        <v>6563564</v>
+        <v>6563533</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4488,13 +4501,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126004770</t>
+          <t>https://artportalen.se/Sighting/126004064</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126004805</v>
+        <v>126004770</v>
       </c>
       <c r="B37" t="n">
         <v>99035</v>
@@ -4533,13 +4546,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>687448</v>
+        <v>687399</v>
       </c>
       <c r="R37" t="n">
-        <v>6563548</v>
+        <v>6563564</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4595,13 +4608,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126004805</t>
+          <t>https://artportalen.se/Sighting/126004770</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126004817</v>
+        <v>126004805</v>
       </c>
       <c r="B38" t="n">
         <v>99035</v>
@@ -4640,10 +4653,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>687473</v>
+        <v>687448</v>
       </c>
       <c r="R38" t="n">
-        <v>6563539</v>
+        <v>6563548</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4702,50 +4715,42 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126004817</t>
+          <t>https://artportalen.se/Sighting/126004805</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126212282</v>
+        <v>126004817</v>
       </c>
       <c r="B39" t="n">
-        <v>99118</v>
+        <v>99035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -4755,13 +4760,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>687344</v>
+        <v>687473</v>
       </c>
       <c r="R39" t="n">
-        <v>6563653</v>
+        <v>6563539</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4785,12 +4790,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4817,55 +4822,63 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126212282</t>
+          <t>https://artportalen.se/Sighting/126004817</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>99519751</v>
+        <v>126212282</v>
       </c>
       <c r="B40" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>V Vargklova Mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>687282</v>
+        <v>687344</v>
       </c>
       <c r="R40" t="n">
-        <v>6563582</v>
+        <v>6563653</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4892,12 +4905,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4924,13 +4937,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99519751</t>
+          <t>https://artportalen.se/Sighting/126212282</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126004216</v>
+        <v>99519751</v>
       </c>
       <c r="B41" t="n">
         <v>106244</v>
@@ -4965,14 +4978,14 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>V Vargklova Mosse, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>687301</v>
+        <v>687282</v>
       </c>
       <c r="R41" t="n">
-        <v>6563579</v>
+        <v>6563582</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4999,12 +5012,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5031,13 +5044,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126004216</t>
+          <t>https://artportalen.se/Sighting/99519751</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126004260</v>
+        <v>126004216</v>
       </c>
       <c r="B42" t="n">
         <v>106244</v>
@@ -5076,10 +5089,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>687243</v>
+        <v>687301</v>
       </c>
       <c r="R42" t="n">
-        <v>6563585</v>
+        <v>6563579</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5138,13 +5151,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126004260</t>
+          <t>https://artportalen.se/Sighting/126004216</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126004295</v>
+        <v>126004260</v>
       </c>
       <c r="B43" t="n">
         <v>106244</v>
@@ -5183,10 +5196,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>687291</v>
+        <v>687243</v>
       </c>
       <c r="R43" t="n">
-        <v>6563610</v>
+        <v>6563585</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5245,13 +5258,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126004295</t>
+          <t>https://artportalen.se/Sighting/126004260</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126004534</v>
+        <v>126004295</v>
       </c>
       <c r="B44" t="n">
         <v>106244</v>
@@ -5281,11 +5294,7 @@
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>knoppbristning</t>
-        </is>
-      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
@@ -5294,10 +5303,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>687349</v>
+        <v>687291</v>
       </c>
       <c r="R44" t="n">
-        <v>6563661</v>
+        <v>6563610</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5356,16 +5365,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126004534</t>
+          <t>https://artportalen.se/Sighting/126004295</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>78194577</v>
+        <v>126004534</v>
       </c>
       <c r="B45" t="n">
-        <v>97989</v>
+        <v>106244</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5373,41 +5382,45 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>knoppbristning</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sävkärrs mosse SO/NP-gränsen, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>687235</v>
+        <v>687349</v>
       </c>
       <c r="R45" t="n">
-        <v>6563600</v>
+        <v>6563661</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5431,17 +5444,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2019-06-02</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2019-06-02</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ett flertal fortf. vid god vigör men många döda och vissna</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5457,24 +5465,24 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78194577</t>
+          <t>https://artportalen.se/Sighting/126004534</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>111689384</v>
+        <v>78194577</v>
       </c>
       <c r="B46" t="n">
         <v>97989</v>
@@ -5509,17 +5517,17 @@
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>S Vargklova mosse, Srm</t>
+          <t>Sävkärrs mosse SO/NP-gränsen, Srm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>687532</v>
+        <v>687235</v>
       </c>
       <c r="R46" t="n">
-        <v>6563517</v>
+        <v>6563600</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5543,12 +5551,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2019-06-02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2019-06-02</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ett flertal fortf. vid god vigör men många döda och vissna</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5564,24 +5577,24 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111689384</t>
+          <t>https://artportalen.se/Sighting/78194577</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121859680</v>
+        <v>111689384</v>
       </c>
       <c r="B47" t="n">
         <v>97989</v>
@@ -5610,16 +5623,20 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>S Vargklova mosse, Srm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>687241</v>
+        <v>687532</v>
       </c>
       <c r="R47" t="n">
-        <v>6563587</v>
+        <v>6563517</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5646,22 +5663,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>11:58</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>11:58</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5670,30 +5677,31 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859680</t>
+          <t>https://artportalen.se/Sighting/111689384</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121859681</v>
+        <v>121859680</v>
       </c>
       <c r="B48" t="n">
         <v>97989</v>
@@ -5728,10 +5736,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>687245</v>
+        <v>687241</v>
       </c>
       <c r="R48" t="n">
-        <v>6563595</v>
+        <v>6563587</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5763,7 +5771,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5773,7 +5781,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5799,16 +5807,16 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859681</t>
+          <t>https://artportalen.se/Sighting/121859680</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121859668</v>
+        <v>121859681</v>
       </c>
       <c r="B49" t="n">
-        <v>97983</v>
+        <v>97989</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5816,16 +5824,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5840,10 +5848,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>687531</v>
+        <v>687245</v>
       </c>
       <c r="R49" t="n">
-        <v>6563515</v>
+        <v>6563595</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5875,7 +5883,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5885,7 +5893,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5911,13 +5919,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859668</t>
+          <t>https://artportalen.se/Sighting/121859681</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121859678</v>
+        <v>121859668</v>
       </c>
       <c r="B50" t="n">
         <v>97983</v>
@@ -5952,10 +5960,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>687239</v>
+        <v>687531</v>
       </c>
       <c r="R50" t="n">
-        <v>6563531</v>
+        <v>6563515</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5987,7 +5995,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5997,12 +6005,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Mycket rikligt.</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6028,13 +6031,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859678</t>
+          <t>https://artportalen.se/Sighting/121859668</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121859679</v>
+        <v>121859678</v>
       </c>
       <c r="B51" t="n">
         <v>97983</v>
@@ -6069,10 +6072,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>687220</v>
+        <v>687239</v>
       </c>
       <c r="R51" t="n">
-        <v>6563556</v>
+        <v>6563531</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6104,7 +6107,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6114,7 +6117,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Mycket rikligt.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6140,13 +6148,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859679</t>
+          <t>https://artportalen.se/Sighting/121859678</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121859683</v>
+        <v>121859679</v>
       </c>
       <c r="B52" t="n">
         <v>97983</v>
@@ -6181,10 +6189,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>687243</v>
+        <v>687220</v>
       </c>
       <c r="R52" t="n">
-        <v>6563593</v>
+        <v>6563556</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6216,7 +6224,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6226,7 +6234,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6252,13 +6260,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859683</t>
+          <t>https://artportalen.se/Sighting/121859679</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126079502</v>
+        <v>121859683</v>
       </c>
       <c r="B53" t="n">
         <v>97983</v>
@@ -6287,23 +6295,19 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>687453</v>
+        <v>687243</v>
       </c>
       <c r="R53" t="n">
-        <v>6563526</v>
+        <v>6563593</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6327,17 +6331,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Rikligt i kärret.</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6346,34 +6355,33 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126079502</t>
+          <t>https://artportalen.se/Sighting/121859683</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121859682</v>
+        <v>126079502</v>
       </c>
       <c r="B54" t="n">
-        <v>97986</v>
+        <v>97983</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6381,16 +6389,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6399,19 +6407,23 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>687243</v>
+        <v>687453</v>
       </c>
       <c r="R54" t="n">
-        <v>6563593</v>
+        <v>6563526</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6435,22 +6447,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:52</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:52</t>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Rikligt i kärret.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6459,33 +6466,34 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859682</t>
+          <t>https://artportalen.se/Sighting/126079502</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126234839</v>
+        <v>121859682</v>
       </c>
       <c r="B55" t="n">
-        <v>99140</v>
+        <v>97986</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6493,50 +6501,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221952</v>
+        <v>221946</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Vargklova mosse S om, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>687489</v>
+        <v>687243</v>
       </c>
       <c r="R55" t="n">
-        <v>6563516</v>
+        <v>6563593</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6563,12 +6555,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6577,31 +6579,30 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234839</t>
+          <t>https://artportalen.se/Sighting/121859682</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126234886</v>
+        <v>126234839</v>
       </c>
       <c r="B56" t="n">
         <v>99140</v>
@@ -6641,7 +6642,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
@@ -6652,10 +6653,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>687464</v>
+        <v>687489</v>
       </c>
       <c r="R56" t="n">
-        <v>6563531</v>
+        <v>6563516</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6714,16 +6715,16 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234886</t>
+          <t>https://artportalen.se/Sighting/126234839</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134487957</v>
+        <v>126234886</v>
       </c>
       <c r="B57" t="n">
-        <v>99217</v>
+        <v>99140</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6748,8 +6749,16 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -6759,17 +6768,17 @@
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Vargklova mosse S om, Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>687245</v>
+        <v>687464</v>
       </c>
       <c r="R57" t="n">
-        <v>6563523</v>
+        <v>6563531</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6793,17 +6802,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>11 i blom samt flera plantor med endast blad.</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6819,16 +6823,132 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126234886</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>134487957</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>687245</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6563523</v>
+      </c>
+      <c r="S58" t="n">
+        <v>25</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>11 i blom samt flera plantor med endast blad.</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134487957</t>
         </is>
@@ -6892,6 +7012,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -3202,7 +3202,7 @@
         <v>135827336</v>
       </c>
       <c r="B25" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -1374,7 +1374,7 @@
         <v>136159865</v>
       </c>
       <c r="B8" t="n">
-        <v>96725</v>
+        <v>96726</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>135827336</v>
       </c>
       <c r="B25" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -1374,7 +1374,7 @@
         <v>136159865</v>
       </c>
       <c r="B8" t="n">
-        <v>96726</v>
+        <v>96727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>135827336</v>
       </c>
       <c r="B25" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -1374,7 +1374,7 @@
         <v>136159865</v>
       </c>
       <c r="B8" t="n">
-        <v>96727</v>
+        <v>96733</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>135827336</v>
       </c>
       <c r="B25" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -1374,7 +1374,7 @@
         <v>136159865</v>
       </c>
       <c r="B8" t="n">
-        <v>96733</v>
+        <v>96734</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>135827336</v>
       </c>
       <c r="B25" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
